--- a/test-data/Templates/SHS/M1 - Create Material type HAWA (GB Agency).xlsx
+++ b/test-data/Templates/SHS/M1 - Create Material type HAWA (GB Agency).xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10419"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10517"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tejavathidoddapaneni/Maextro_AutomationApp/test-data/Templates/SHS/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E18AE41-23C1-1E4E-AE28-463ECA575AF6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{332C068C-C54F-CC4E-A70C-E8B199183FF2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17180" activeTab="1" xr2:uid="{9B722DE1-D4F2-8E4B-A1FC-B7FBF3A04462}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17180" xr2:uid="{9B722DE1-D4F2-8E4B-A1FC-B7FBF3A04462}"/>
   </bookViews>
   <sheets>
     <sheet name="MXT_HDR" sheetId="1" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="953" uniqueCount="212">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="950" uniqueCount="212">
   <si>
     <t>Object</t>
   </si>
@@ -1195,9 +1195,6 @@
       <c r="D7" t="s">
         <v>71</v>
       </c>
-      <c r="F7" t="s">
-        <v>71</v>
-      </c>
     </row>
     <row r="8" spans="1:8" ht="17" x14ac:dyDescent="0.2">
       <c r="A8" s="3">
@@ -1254,9 +1251,6 @@
       <c r="D11" t="s">
         <v>71</v>
       </c>
-      <c r="F11" t="s">
-        <v>71</v>
-      </c>
     </row>
     <row r="12" spans="1:8" ht="51" x14ac:dyDescent="0.2">
       <c r="A12" s="3">
@@ -1271,9 +1265,6 @@
       <c r="D12" t="s">
         <v>71</v>
       </c>
-      <c r="F12" t="s">
-        <v>71</v>
-      </c>
     </row>
     <row r="13" spans="1:8" ht="17" x14ac:dyDescent="0.2">
       <c r="A13" s="3">
@@ -1294,9 +1285,6 @@
     </row>
   </sheetData>
   <dataValidations count="4">
-    <dataValidation type="list" showInputMessage="1" showErrorMessage="1" sqref="D6:D13" xr:uid="{58227CB0-C6D9-A247-A15C-D0FCE8718EAF}">
-      <formula1>"Save,Skip,Approve,Reject -&gt; Approve"</formula1>
-    </dataValidation>
     <dataValidation type="list" showInputMessage="1" showErrorMessage="1" sqref="D2" xr:uid="{480D1B17-2E92-9240-8BCE-1DA3147CCDB2}">
       <formula1>"New Material"</formula1>
     </dataValidation>
@@ -1305,6 +1293,9 @@
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F2" xr:uid="{867B6D3F-F6EA-6D45-89A3-70B9CE3A4229}">
       <formula1>"Low,Medium,High"</formula1>
+    </dataValidation>
+    <dataValidation type="list" showInputMessage="1" showErrorMessage="1" sqref="D6:D13" xr:uid="{938667EF-0630-FF44-921C-A4A77E8A7629}">
+      <formula1>"Save,Skip,Approve,Skip -&gt; Save,Skip -&gt; Approve,Reject -&gt; Approve"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
